--- a/PAMF_DIG F2 - monthly2026-07-15.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-15.xlsx
@@ -633,7 +633,7 @@
         <v>0.09</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>0.09</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>0.09</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>0.09</v>
       </c>
       <c r="N67" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -8152,7 +8152,7 @@
         <v>0.09</v>
       </c>
       <c r="N106" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-15.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-15.xlsx
@@ -7495,7 +7495,7 @@
         <v>0.09</v>
       </c>
       <c r="N97" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>0.09</v>
       </c>
       <c r="N161" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O161" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>0.09</v>
       </c>
       <c r="N166" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>0.09</v>
       </c>
       <c r="N194" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
